--- a/data/trans_orig/P36BPD09_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40864</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64306</t>
+          <t>63185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70445</t>
+          <t>69972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103502</t>
+          <t>101305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287502</t>
+          <t>285267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329878</t>
+          <t>326484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415224</t>
+          <t>415190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458415</t>
+          <t>456324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716589</t>
+          <t>714747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774338</t>
+          <t>771817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152704</t>
+          <t>154969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192502</t>
+          <t>192522</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246332</t>
+          <t>246740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>288249</t>
+          <t>287188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>410714</t>
+          <t>412288</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>468330</t>
+          <t>469162</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101096</t>
+          <t>108658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191155</t>
+          <t>196664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100267</t>
+          <t>97278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163053</t>
+          <t>163360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233513</t>
+          <t>232163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>342264</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>948332</t>
+          <t>947455</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1539525</t>
+          <t>1538187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>926225</t>
+          <t>970667</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1508948</t>
+          <t>1509885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2078408</t>
+          <t>2161461</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2986322</t>
+          <t>2990867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>576193</t>
+          <t>575701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1233284</t>
+          <t>1222249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>578513</t>
+          <t>576634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1198412</t>
+          <t>1173047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1208804</t>
+          <t>1209578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2216213</t>
+          <t>2095243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39105</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45182</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75113</t>
+          <t>72469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>91764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>130824</t>
+          <t>132494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401819</t>
+          <t>400345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>453070</t>
+          <t>454406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>423600</t>
+          <t>421985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468301</t>
+          <t>465378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>836478</t>
+          <t>840035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>904907</t>
+          <t>905125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145139</t>
+          <t>142624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193790</t>
+          <t>191589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>137957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174565</t>
+          <t>175278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>292099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355945</t>
+          <t>350580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182037</t>
+          <t>186497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282029</t>
+          <t>279188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198187</t>
+          <t>198666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276950</t>
+          <t>277926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413691</t>
+          <t>409767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>540798</t>
+          <t>535193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1652503</t>
+          <t>1631211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2277571</t>
+          <t>2277913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1856267</t>
+          <t>1707858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2396784</t>
+          <t>2392235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3716483</t>
+          <t>3731986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4625522</t>
+          <t>4622533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>913724</t>
+          <t>914198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1620588</t>
+          <t>1626893</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>996526</t>
+          <t>1000914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1589192</t>
+          <t>1738676</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1961414</t>
+          <t>1953404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2982047</t>
+          <t>2956933</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD09_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43676</t>
+          <t>53430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50552</t>
+          <t>55534</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>69195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83477</t>
+          <t>93926</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69972</t>
+          <t>78719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101305</t>
+          <t>112089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308786</t>
+          <t>346693</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285267</t>
+          <t>322219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326484</t>
+          <t>368070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>436100</t>
+          <t>477722</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415190</t>
+          <t>455163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456324</t>
+          <t>498241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>744886</t>
+          <t>824416</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714747</t>
+          <t>791762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771817</t>
+          <t>854415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172548</t>
+          <t>192668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154969</t>
+          <t>172141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192522</t>
+          <t>215265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>266214</t>
+          <t>286040</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246740</t>
+          <t>265099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287188</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>438762</t>
+          <t>478707</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>412288</t>
+          <t>448651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>469162</t>
+          <t>508899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514259</t>
+          <t>577753</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514259</t>
+          <t>577753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514259</t>
+          <t>577753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>752866</t>
+          <t>819296</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>752866</t>
+          <t>819296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>752866</t>
+          <t>819296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267125</t>
+          <t>1397049</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267125</t>
+          <t>1397049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267125</t>
+          <t>1397049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154330</t>
+          <t>177643</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108658</t>
+          <t>149019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196664</t>
+          <t>209643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134923</t>
+          <t>158611</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>136820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163360</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>289253</t>
+          <t>336255</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232163</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>373005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1358142</t>
+          <t>1467753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>947455</t>
+          <t>1415379</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1538187</t>
+          <t>1517869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1349031</t>
+          <t>1436065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>970667</t>
+          <t>1396057</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1509885</t>
+          <t>1476060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2707173</t>
+          <t>2903818</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2161461</t>
+          <t>2838337</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2990867</t>
+          <t>2970583</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>773137</t>
+          <t>580338</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>575701</t>
+          <t>532973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1222249</t>
+          <t>631007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>751432</t>
+          <t>574297</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>576634</t>
+          <t>536674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1173047</t>
+          <t>611906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1524569</t>
+          <t>1154635</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1209578</t>
+          <t>1094803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2095243</t>
+          <t>1210943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2225735</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2225735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2225735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2235386</t>
+          <t>2168973</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2235386</t>
+          <t>2168973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2235386</t>
+          <t>2168973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4520995</t>
+          <t>4394708</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4520995</t>
+          <t>4394708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4520995</t>
+          <t>4394708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68448</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>66357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72469</t>
+          <t>84405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>109877</t>
+          <t>122856</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91764</t>
+          <t>102117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132494</t>
+          <t>145831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>427513</t>
+          <t>464438</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>400345</t>
+          <t>434163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>454406</t>
+          <t>491316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>445819</t>
+          <t>492947</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>421985</t>
+          <t>467928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>465378</t>
+          <t>513781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>873332</t>
+          <t>957385</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>840035</t>
+          <t>917789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>905125</t>
+          <t>991505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>167450</t>
+          <t>190649</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142624</t>
+          <t>165783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191589</t>
+          <t>217144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>154844</t>
+          <t>174076</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137957</t>
+          <t>155133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175278</t>
+          <t>196965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>322293</t>
+          <t>364725</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292099</t>
+          <t>330580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350580</t>
+          <t>396491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>238916</t>
+          <t>272535</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186497</t>
+          <t>234702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279188</t>
+          <t>308157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>243692</t>
+          <t>280502</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198666</t>
+          <t>250500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>277926</t>
+          <t>311684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>482608</t>
+          <t>553037</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409767</t>
+          <t>504662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>535193</t>
+          <t>607190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2094441</t>
+          <t>2278885</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1631211</t>
+          <t>2219128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2277913</t>
+          <t>2346014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2230950</t>
+          <t>2406735</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1707858</t>
+          <t>2352810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2392235</t>
+          <t>2456859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4325391</t>
+          <t>4685620</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3731986</t>
+          <t>4608054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4622533</t>
+          <t>4770821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1113135</t>
+          <t>963655</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>914198</t>
+          <t>901164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1626893</t>
+          <t>1025183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1172489</t>
+          <t>1034413</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1000914</t>
+          <t>987770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1738676</t>
+          <t>1081842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2285624</t>
+          <t>1998068</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1953404</t>
+          <t>1917864</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2956933</t>
+          <t>2075988</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3446491</t>
+          <t>3515075</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3446491</t>
+          <t>3515075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3446491</t>
+          <t>3515075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3647132</t>
+          <t>3721650</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3647132</t>
+          <t>3721650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3647132</t>
+          <t>3721650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7093623</t>
+          <t>7236725</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7093623</t>
+          <t>7236725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7093623</t>
+          <t>7236725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
